--- a/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,29</t>
+          <t>-3,06; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,0</t>
+          <t>-4,71; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,53</t>
+          <t>1,16; 8,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,22</t>
+          <t>-1,92; 4,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,65</t>
+          <t>-3,96; 0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 9,9</t>
+          <t>1,02; 9,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,05</t>
+          <t>-1,74; 2,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,09</t>
+          <t>-3,21; 0,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,19</t>
+          <t>1,95; 7,57</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,47; —</t>
+          <t>-11,5; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 1740,76</t>
+          <t>-11,05; 2059,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,81; 393,43</t>
+          <t>-74,72; 461,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,6; 1179,11</t>
+          <t>40,27; 1182,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,96</t>
+          <t>0,63; 6,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,23</t>
+          <t>-0,75; 4,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,71</t>
+          <t>0,54; 5,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,95</t>
+          <t>-4,05; 3,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,08</t>
+          <t>-5,1; 1,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 7,5</t>
+          <t>-0,39; 7,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,93</t>
+          <t>-0,99; 3,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,77</t>
+          <t>-2,29; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,78</t>
+          <t>0,79; 5,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,5; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,91; —</t>
+          <t>-72,58; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,82; —</t>
+          <t>-17,99; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,0; 137,76</t>
+          <t>-69,74; 143,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 56,29</t>
+          <t>-81,59; 69,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 322,41</t>
+          <t>-14,6; 330,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 246,25</t>
+          <t>-30,65; 227,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,79; 125,42</t>
+          <t>-59,83; 111,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 365,07</t>
+          <t>17,23; 362,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,7</t>
+          <t>-5,57; 0,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,25</t>
+          <t>-6,19; -0,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,29</t>
+          <t>-1,02; 7,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,87</t>
+          <t>-4,61; 4,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 2,27</t>
+          <t>-5,96; 2,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 9,74</t>
+          <t>-2,58; 9,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,39</t>
+          <t>-3,55; 1,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,33</t>
+          <t>-4,72; 0,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,53</t>
+          <t>-0,69; 7,0</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 188,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 520,42</t>
+          <t>-25,6; 557,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 181,66</t>
+          <t>-70,83; 237,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-88,08; 114,63</t>
+          <t>-87,08; 207,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 430,61</t>
+          <t>-51,67; 419,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 65,16</t>
+          <t>-68,82; 90,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,46; 27,25</t>
+          <t>-88,42; 34,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 244,38</t>
+          <t>-20,11; 299,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,02</t>
+          <t>-0,92; 5,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,96</t>
+          <t>0,44; 7,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,56</t>
+          <t>0,23; 6,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,85</t>
+          <t>-2,87; 4,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,13</t>
+          <t>-4,01; 2,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,95</t>
+          <t>-3,83; 3,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,5</t>
+          <t>-1,1; 3,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,03</t>
+          <t>-0,72; 4,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,59</t>
+          <t>-0,82; 3,55</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 1002,38</t>
+          <t>-51,21; 1095,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 1299,39</t>
+          <t>-13,73; 1156,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 1082,56</t>
+          <t>-11,47; 1282,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 230,88</t>
+          <t>-58,49; 269,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,87; 148,24</t>
+          <t>-75,25; 159,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 213,71</t>
+          <t>-74,49; 197,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 217,11</t>
+          <t>-38,27; 238,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 237,54</t>
+          <t>-31,06; 236,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 207,33</t>
+          <t>-27,7; 221,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,63</t>
+          <t>-0,48; 2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,38</t>
+          <t>-0,54; 2,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,31</t>
+          <t>1,63; 5,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,01</t>
+          <t>-1,6; 2,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,43</t>
+          <t>-2,81; 0,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,89</t>
+          <t>0,5; 4,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,79</t>
+          <t>-0,67; 1,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,91</t>
+          <t>-1,29; 0,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,44</t>
+          <t>1,62; 4,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 226,97</t>
+          <t>-23,61; 226,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 213,54</t>
+          <t>-22,92; 227,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61,9; 479,42</t>
+          <t>57,82; 471,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 83,57</t>
+          <t>-38,18; 78,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 20,28</t>
+          <t>-65,35; 21,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,16; 184,63</t>
+          <t>8,32; 192,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 85,41</t>
+          <t>-21,31; 86,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-40,84; 44,8</t>
+          <t>-41,62; 48,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,08; 211,19</t>
+          <t>46,81; 224,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,33</t>
+          <t>-2,99; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,0</t>
+          <t>-4,26; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 8,46</t>
+          <t>1,02; 7,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,04</t>
+          <t>-2,15; 3,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,82</t>
+          <t>-3,66; 0,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,68</t>
+          <t>0,99; 9,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,1</t>
+          <t>-1,83; 2,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,08</t>
+          <t>-2,98; 0,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,57</t>
+          <t>1,85; 7,55</t>
         </is>
       </c>
     </row>
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,5; —</t>
+          <t>-25,99; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-91,91; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-13,64; 1515,65</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-82,99; 322,93</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-11,05; 2059,81</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-74,72; 461,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,27; 1182,3</t>
+          <t>42,14; 1198,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,97</t>
+          <t>0,7; 7,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,01</t>
+          <t>-0,57; 4,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,62</t>
+          <t>0,57; 5,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,06</t>
+          <t>-4,46; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,4</t>
+          <t>-5,44; 1,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 7,81</t>
+          <t>-0,52; 7,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,98</t>
+          <t>-1,07; 4,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,81</t>
+          <t>-2,31; 1,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,74</t>
+          <t>0,93; 5,97</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,7; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-72,58; —</t>
+          <t>-74,06; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,99; —</t>
+          <t>-13,13; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 143,47</t>
+          <t>-71,27; 135,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 69,65</t>
+          <t>-83,35; 67,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 330,17</t>
+          <t>-11,87; 379,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 227,9</t>
+          <t>-33,74; 273,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 111,91</t>
+          <t>-62,86; 122,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 362,13</t>
+          <t>12,88; 340,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,44</t>
+          <t>-5,14; 0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -0,58</t>
+          <t>-6,27; -0,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 7,2</t>
+          <t>-1,57; 7,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 4,17</t>
+          <t>-4,43; 3,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 2,34</t>
+          <t>-6,09; 1,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 9,18</t>
+          <t>-2,41; 9,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,81</t>
+          <t>-3,56; 1,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,44</t>
+          <t>-4,39; 0,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,0</t>
+          <t>-0,64; 6,87</t>
         </is>
       </c>
     </row>
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 557,8</t>
+          <t>-46,15; 553,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 237,04</t>
+          <t>-68,07; 179,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,08; 207,69</t>
+          <t>-89,27; 104,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 419,78</t>
+          <t>-49,29; 366,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 90,08</t>
+          <t>-71,8; 65,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,42; 34,09</t>
+          <t>-86,68; 34,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 299,12</t>
+          <t>-16,2; 291,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,87</t>
+          <t>-1,08; 6,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,69</t>
+          <t>0,51; 7,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,67</t>
+          <t>0,08; 6,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,17</t>
+          <t>-3,05; 4,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 2,31</t>
+          <t>-3,88; 2,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,25</t>
+          <t>-3,63; 2,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 3,79</t>
+          <t>-1,12; 3,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,0</t>
+          <t>-0,81; 3,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,55</t>
+          <t>-0,87; 3,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,21; 1095,72</t>
+          <t>-52,98; 855,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 1156,65</t>
+          <t>-9,58; 1264,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 1282,99</t>
+          <t>-13,56; 858,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 269,42</t>
+          <t>-66,04; 239,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,25; 159,72</t>
+          <t>-77,44; 160,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 197,82</t>
+          <t>-72,85; 189,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 238,93</t>
+          <t>-35,68; 237,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 236,77</t>
+          <t>-31,73; 219,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 221,1</t>
+          <t>-25,71; 235,87</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,69</t>
+          <t>-0,43; 2,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,43</t>
+          <t>-0,57; 2,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,06</t>
+          <t>1,78; 5,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,02</t>
+          <t>-1,73; 2,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,42</t>
+          <t>-2,96; 0,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,98</t>
+          <t>0,62; 5,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,69</t>
+          <t>-0,58; 1,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,97</t>
+          <t>-1,33; 0,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,55</t>
+          <t>1,68; 4,47</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 226,94</t>
+          <t>-21,71; 250,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 227,7</t>
+          <t>-27,8; 207,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57,82; 471,35</t>
+          <t>60,79; 451,16</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 78,49</t>
+          <t>-41,21; 81,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 21,11</t>
+          <t>-67,88; 22,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,32; 192,01</t>
+          <t>12,54; 202,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 86,76</t>
+          <t>-18,64; 97,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 48,6</t>
+          <t>-41,2; 46,21</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46,81; 224,96</t>
+          <t>51,97; 211,4</t>
         </is>
       </c>
     </row>
